--- a/backend/local_storage/default/employees.xlsx
+++ b/backend/local_storage/default/employees.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,11 @@
           <t>emergency_number</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>reporting_manager</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -553,6 +558,11 @@
       <c r="M2" t="n">
         <v>0</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Mahesh</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -583,10 +593,8 @@
           <t>avinash@gmail.com</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>7058061264</t>
-        </is>
+      <c r="G3" t="n">
+        <v>7058061264</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -598,14 +606,119 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
+      <c r="J3" t="n">
+        <v>3500</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mahesh</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RV003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mahesh@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1234567890</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RV004</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>rahul@example.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Kiran Aglawe</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
